--- a/jira_clone/agile_daily_tracker.xlsx
+++ b/jira_clone/agile_daily_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maamoun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3715DB-7952-4F37-8681-5BA8AE26C3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD0F16B-896D-4DAB-AA0C-1CF3A4E36E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,10 +273,6 @@
 Time commit + push + update prompt text and set the tas done : 10 min</t>
   </si>
   <si>
-    <t>branch : manage_ticket_tracking
-commit : ae26070df27f40cbe4d9d46dfa0c085b6099cb9c</t>
-  </si>
-  <si>
     <t>add Ticket Link To</t>
   </si>
   <si>
@@ -307,10 +303,6 @@
   </si>
   <si>
     <t xml:space="preserve">ticket link </t>
-  </si>
-  <si>
-    <t>branch : manage_ticket_tracking
-commit : 7c8f41af75042c1b442a762c4302179f9573c30b</t>
   </si>
   <si>
     <t xml:space="preserve">Plan to change end status </t>
@@ -391,19 +383,27 @@
 - manageTicketTracking.js : _loadData method </t>
   </si>
   <si>
-    <t>branch : manage_ticket_tracking
+    <t>Task 16</t>
+  </si>
+  <si>
+    <t>P014 - P015 - P016</t>
+  </si>
+  <si>
+    <t>commit hash : 35b63489ea349ff172c16329adc6603cc1a7256f
+commit message : 5/7/2026-sprint1-[task15-task16]</t>
+  </si>
+  <si>
+    <t>branch : manage_ticket_page
 commit hash : 501b221833fc2b4d09bc60bf11577d8c8379bb5c
 commit message : watch blue change in new_er_diagram or Untitled Diagram-Page2.drawio.png</t>
   </si>
   <si>
-    <t>Task 16</t>
-  </si>
-  <si>
-    <t>P014 - P015 - P016</t>
-  </si>
-  <si>
-    <t>commit hash : 35b63489ea349ff172c16329adc6603cc1a7256f
-commit message : 5/7/2026-sprint1-[task15-task16]</t>
+    <t>branch : manage_ticket_page
+commit : ae26070df27f40cbe4d9d46dfa0c085b6099cb9c</t>
+  </si>
+  <si>
+    <t>branch : manage_ticket_page
+commit : 7c8f41af75042c1b442a762c4302179f9573c30b</t>
   </si>
 </sst>
 </file>
@@ -993,13 +993,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4" s="5">
         <v>2</v>
@@ -1011,7 +1011,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
@@ -1028,7 +1028,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>42</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
@@ -1250,7 +1250,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>42</v>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1278,22 +1278,22 @@
         <v>12</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H14" s="5">
         <v>0.3</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -1308,13 +1308,13 @@
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H15" s="5">
         <v>0.1</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1338,22 +1338,22 @@
         <v>14</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H16" s="5">
         <v>0.3</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K16" s="3"/>
     </row>
@@ -1368,25 +1368,25 @@
         <v>15</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H17" s="5">
         <v>0.4</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="79.2" x14ac:dyDescent="0.3">
@@ -1404,7 +1404,7 @@
         <v>42</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H18" s="5">
         <v>0.3</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">

--- a/jira_clone/agile_daily_tracker.xlsx
+++ b/jira_clone/agile_daily_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maamoun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD0F16B-896D-4DAB-AA0C-1CF3A4E36E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B6B31D-39A4-4E87-BE27-C2D1D33849EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Log'!$A$1:$K$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Log'!$A$1:$K$249</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -404,6 +404,72 @@
   <si>
     <t>branch : manage_ticket_page
 commit : 7c8f41af75042c1b442a762c4302179f9573c30b</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>show : 
+- total story point for sprint 
+- total ended story point for sprint</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>`- update er
+- update erd 
+- plan for development</t>
+  </si>
+  <si>
+    <t>update er</t>
+  </si>
+  <si>
+    <t xml:space="preserve">update erd </t>
+  </si>
+  <si>
+    <t>plan for development</t>
+  </si>
+  <si>
+    <t>branch name : manage_ticket_page
+commit hash : a8193931ef03369bdd50760f6265aa6c78f6ea7e
+commit message : 5/6/2026-sprint1-Task18</t>
+  </si>
+  <si>
+    <t>create new 2 field  in sprint object</t>
+  </si>
+  <si>
+    <t>branch name : manage_ticket_page
+commit hash : 6890797f7bb9ab5798e19611670a5f55f8072574
+commit message : 5/6/2026-sprint1-Task19</t>
+  </si>
+  <si>
+    <t>task 18 , task 19 , task 20</t>
+  </si>
+  <si>
+    <t>show total story points and ended story points in manageTicketTracking page</t>
+  </si>
+  <si>
+    <t>show total story points and ended story points in manageBacklog page</t>
+  </si>
+  <si>
+    <t>Task 21-22</t>
+  </si>
+  <si>
+    <t>update frontEnd : When sprint hit the end status : 
+   - ended story point will be increased by the ticket story point if the transaction  sucees.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Manage Ticket Tracking Page : 
+ - show the total story point 
+ - show the ended total story point 
+For Manage Backlog Page : 
+ in each sprint container : 
+    - show the total story point 
+    - show the ended total story point 
+When ticket hit the end status : 
+   - ended story point will be increased by the ticket story point if the transaction  sucees.
+</t>
   </si>
 </sst>
 </file>
@@ -539,7 +605,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -856,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K250"/>
+  <dimension ref="A1:K249"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -912,7 +985,7 @@
         <v>46146</v>
       </c>
       <c r="B2" s="3" t="str">
-        <f t="shared" ref="B2:B65" si="0">IF(A2="","",TEXT(A2,"dddd"))</f>
+        <f t="shared" ref="B2:B64" si="0">IF(A2="","",TEXT(A2,"dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="C2" s="3">
@@ -1138,20 +1211,38 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+    <row r="9" spans="1:11" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>8</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="K9" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46147</v>
       </c>
@@ -1162,369 +1253,456 @@
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="5">
-        <v>1</v>
-      </c>
+      <c r="H10" s="5"/>
       <c r="I10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="5"/>
+      <c r="G11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.2</v>
+      </c>
       <c r="I11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>46148</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <v>10</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>67</v>
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="5">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
       <c r="D13" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="H13" s="5">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4">
-        <v>12</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C15" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
       <c r="D15" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H15" s="5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C16" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" ht="107.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
       <c r="D16" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H16" s="5">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" ht="107.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C17" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
       <c r="D17" s="4">
-        <v>15</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>83</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H17" s="5">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>87</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C18" s="3"/>
+    <row r="18" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
       <c r="D18" s="4">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>18</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4">
+        <v>19</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="G20" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4" t="str">
-        <f>IF(A19="","",COUNTIF($A$2:A19,A19))</f>
-        <v/>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
-        <f>IF(A20="","",COUNTIF($A$2:A20,A20))</f>
-        <v/>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4" t="str">
-        <f>IF(A21="","",COUNTIF($A$2:A21,A21))</f>
-        <v/>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
+      <c r="K20" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>20</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
-        <f>IF(A22="","",COUNTIF($A$2:A22,A22))</f>
-        <v/>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+    <row r="22" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>21</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="G22" s="3"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4" t="str">
-        <f>IF(A23="","",COUNTIF($A$2:A23,A23))</f>
-        <v/>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+    <row r="23" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4">
+        <v>22</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="3"/>
+      <c r="H23" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
-        <f>IF(A24="","",COUNTIF($A$2:A24,A24))</f>
-        <v/>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+    <row r="24" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4">
+        <v>23</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="5"/>
       <c r="I24" s="3"/>
@@ -2294,7 +2472,7 @@
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B65:B128" si="1">IF(A65="","",TEXT(A65,"dddd"))</f>
         <v/>
       </c>
       <c r="C65" s="3"/>
@@ -2313,7 +2491,7 @@
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="3" t="str">
-        <f t="shared" ref="B66:B129" si="1">IF(A66="","",TEXT(A66,"dddd"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C66" s="3"/>
@@ -3510,7 +3688,7 @@
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="2"/>
       <c r="B129" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B129:B192" si="2">IF(A129="","",TEXT(A129,"dddd"))</f>
         <v/>
       </c>
       <c r="C129" s="3"/>
@@ -3529,7 +3707,7 @@
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2"/>
       <c r="B130" s="3" t="str">
-        <f t="shared" ref="B130:B193" si="2">IF(A130="","",TEXT(A130,"dddd"))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C130" s="3"/>
@@ -4726,7 +4904,7 @@
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="2"/>
       <c r="B193" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B193:B249" si="3">IF(A193="","",TEXT(A193,"dddd"))</f>
         <v/>
       </c>
       <c r="C193" s="3"/>
@@ -4745,7 +4923,7 @@
     <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="2"/>
       <c r="B194" s="3" t="str">
-        <f t="shared" ref="B194:B250" si="3">IF(A194="","",TEXT(A194,"dddd"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C194" s="3"/>
@@ -5806,52 +5984,38 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A250" s="2"/>
-      <c r="B250" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="C250" s="3"/>
-      <c r="D250" s="4" t="str">
-        <f>IF(A250="","",COUNTIF($A$2:A250,A250))</f>
-        <v/>
-      </c>
-      <c r="E250" s="3"/>
-      <c r="F250" s="3"/>
-      <c r="G250" s="3"/>
-      <c r="H250" s="5"/>
-      <c r="I250" s="3"/>
-      <c r="J250" s="3"/>
-      <c r="K250" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K250" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="A2:K250">
-    <cfRule type="expression" dxfId="7" priority="2">
+  <autoFilter ref="A1:K249" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="A2:K8 A10:K249">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>AND($A2&lt;&gt;"",$A2&lt;&gt;$A1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I250">
-    <cfRule type="expression" dxfId="6" priority="3">
+  <conditionalFormatting sqref="I2:I249">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$I2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$I2="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$I2="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$I2="Cancelled"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A9:K9">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>AND($A9&lt;&gt;"",$A9&lt;&gt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="I2:I250" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I249" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Done,Blocked,Cancelled"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F250" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F249" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Planning,Design,Development,Testing,Documentation,Meeting,Research,Setup,Deployment,Other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6021,13 +6185,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F20">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$F2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$F2="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$F2="Delayed"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6064,8 +6228,8 @@
         <v>29</v>
       </c>
       <c r="B3" s="9">
-        <f>SUM('Daily Log'!H2:H250)</f>
-        <v>13.220000000000002</v>
+        <f>SUM('Daily Log'!H2:H249)</f>
+        <v>14.120000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6073,8 +6237,8 @@
         <v>30</v>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA('Daily Log'!E2:E250)</f>
-        <v>15</v>
+        <f>COUNTA('Daily Log'!E2:E249)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6082,8 +6246,8 @@
         <v>31</v>
       </c>
       <c r="B5" s="11">
-        <f>SUMPRODUCT(('Daily Log'!A2:A250&lt;&gt;"")/COUNTIF('Daily Log'!A2:A250,'Daily Log'!A2:A250&amp;""))</f>
-        <v>3.0000000000000004</v>
+        <f>SUMPRODUCT(('Daily Log'!A2:A249&lt;&gt;"")/COUNTIF('Daily Log'!A2:A249,'Daily Log'!A2:A249&amp;""))</f>
+        <v>3.0000000000000031</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6092,7 +6256,7 @@
       </c>
       <c r="B6" s="9">
         <f>IFERROR(B4/B5,0)</f>
-        <v>4.9999999999999991</v>
+        <v>7.3333333333333259</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6101,7 +6265,7 @@
       </c>
       <c r="B7" s="9">
         <f>IFERROR(B3/B5,0)</f>
-        <v>4.4066666666666672</v>
+        <v>4.7066666666666626</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6109,8 +6273,8 @@
         <v>34</v>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF('Daily Log'!I2:I250,"Done")</f>
-        <v>11</v>
+        <f>COUNTIF('Daily Log'!I2:I249,"Done")</f>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -6118,8 +6282,8 @@
         <v>35</v>
       </c>
       <c r="B9" s="10">
-        <f>COUNTIF('Daily Log'!I2:I250,"In Progress")</f>
-        <v>0</v>
+        <f>COUNTIF('Daily Log'!I2:I249,"In Progress")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -6127,8 +6291,8 @@
         <v>36</v>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF('Daily Log'!I2:I250,"Blocked")</f>
-        <v>3</v>
+        <f>COUNTIF('Daily Log'!I2:I249,"Blocked")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -6137,7 +6301,7 @@
       </c>
       <c r="B11" s="12">
         <f>IFERROR(B8/B4,0)</f>
-        <v>0.73333333333333328</v>
+        <v>0.68181818181818177</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -6153,15 +6317,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A14,'Daily Log'!H2:H250)</f>
-        <v>3.6999999999999997</v>
+        <f>SUMIF('Daily Log'!F2:F249,A14,'Daily Log'!H2:H249)</f>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="9">
-        <f>SUMIF('Daily Log'!C2:C250,1,'Daily Log'!H2:H250)</f>
-        <v>9.82</v>
+        <f>SUMIF('Daily Log'!C2:C249,1,'Daily Log'!H2:H249)</f>
+        <v>14.120000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -6169,14 +6333,14 @@
         <v>15</v>
       </c>
       <c r="B15" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A15,'Daily Log'!H2:H250)</f>
-        <v>0.4</v>
+        <f>SUMIF('Daily Log'!F2:F249,A15,'Daily Log'!H2:H249)</f>
+        <v>0.5</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>41</v>
       </c>
       <c r="E15" s="9">
-        <f>SUMIF('Daily Log'!C2:C250,2,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!C2:C249,2,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6185,14 +6349,14 @@
         <v>42</v>
       </c>
       <c r="B16" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A16,'Daily Log'!H2:H250)</f>
-        <v>8</v>
+        <f>SUMIF('Daily Log'!F2:F249,A16,'Daily Log'!H2:H249)</f>
+        <v>8.3999999999999986</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E16" s="9">
-        <f>SUMIF('Daily Log'!C2:C250,3,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!C2:C249,3,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6201,14 +6365,14 @@
         <v>44</v>
       </c>
       <c r="B17" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A17,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!F2:F249,A17,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="9">
-        <f>SUMIF('Daily Log'!C2:C250,4,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!C2:C249,4,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6217,14 +6381,14 @@
         <v>46</v>
       </c>
       <c r="B18" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A18,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!F2:F249,A18,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E18" s="9">
-        <f>SUMIF('Daily Log'!C2:C250,5,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!C2:C249,5,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6233,14 +6397,14 @@
         <v>11</v>
       </c>
       <c r="B19" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A19,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!F2:F249,A19,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E19" s="9">
-        <f>SUMIF('Daily Log'!C2:C250,6,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!C2:C249,6,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6249,7 +6413,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A20,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!F2:F249,A20,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6258,7 +6422,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A21,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!F2:F249,A21,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6267,7 +6431,7 @@
         <v>49</v>
       </c>
       <c r="B22" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A22,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!F2:F249,A22,'Daily Log'!H2:H249)</f>
         <v>0</v>
       </c>
     </row>
@@ -6276,7 +6440,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="9">
-        <f>SUMIF('Daily Log'!F2:F250,A23,'Daily Log'!H2:H250)</f>
+        <f>SUMIF('Daily Log'!F2:F249,A23,'Daily Log'!H2:H249)</f>
         <v>1.1200000000000001</v>
       </c>
     </row>
